--- a/video-editor/editor_tracker.xlsx
+++ b/video-editor/editor_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H264"/>
+  <dimension ref="A1:H282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="109" customWidth="1" min="6" max="6"/>
-    <col width="86" customWidth="1" min="7" max="7"/>
+    <col width="81" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -558,7 +558,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:12</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -6953,12 +6953,12 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_81_Honda_WR-V\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:52</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:12</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
@@ -7033,22 +7033,22 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_82_Honda_Jazz\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:19</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Honda Brio</t>
+          <t>Honda Jazz</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -7068,27 +7068,27 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>output\100_popular_cars_in_India_83_Honda_Brio\Honda_Brio.mp4</t>
+          <t>output\100_popular_cars_in_India_82_Honda_Jazz\Honda_Jazz.mp4</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_83_Honda_Brio\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:26</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Honda Civic</t>
+          <t>Honda Brio</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -7108,27 +7108,27 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>output\100_popular_cars_in_India_84_Honda_Civic\Honda_Civic.mp4</t>
+          <t>output\100_popular_cars_in_India_83_Honda_Brio\Honda_Brio.mp4</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_84_Honda_Civic\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:35</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Honda CR-V</t>
+          <t>Honda Brio</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -7148,27 +7148,27 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>output\100_popular_cars_in_India_85_Honda_CR-V\Honda_CR-V.mp4</t>
+          <t>output\100_popular_cars_in_India_83_Honda_Brio\Honda_Brio.mp4</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_85_Honda_CR-V\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:43</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Honda Accord</t>
+          <t>Honda Civic</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -7188,27 +7188,27 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>output\100_popular_cars_in_India_86_Honda_Accord\Honda_Accord.mp4</t>
+          <t>output\100_popular_cars_in_India_84_Honda_Civic\Honda_Civic.mp4</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_86_Honda_Accord\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:51</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Volkswagen Virtus</t>
+          <t>Honda Civic</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -7228,27 +7228,27 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>output\100_popular_cars_in_India_87_Volkswagen_Virtus\Volkswagen_Virtus.mp4</t>
+          <t>output\100_popular_cars_in_India_84_Honda_Civic\Honda_Civic.mp4</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_87_Volkswagen_Virtus\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:59</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Volkswagen Taigun</t>
+          <t>Honda CR-V</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -7268,27 +7268,27 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>output\100_popular_cars_in_India_88_Volkswagen_Taigun\Volkswagen_Taigun.mp4</t>
+          <t>output\100_popular_cars_in_India_85_Honda_CR-V\Honda_CR-V.mp4</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_88_Volkswagen_Taigun\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:48:07</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Volkswagen Polo</t>
+          <t>Honda CR-V</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -7308,27 +7308,27 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>output\100_popular_cars_in_India_89_Volkswagen_Polo\Volkswagen_Polo.mp4</t>
+          <t>output\100_popular_cars_in_India_85_Honda_CR-V\Honda_CR-V.mp4</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_89_Volkswagen_Polo\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:48:16</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Volkswagen Vento</t>
+          <t>Honda Accord</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -7348,37 +7348,37 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>output\100_popular_cars_in_India_90_Volkswagen_Vento\Volkswagen_Vento.mp4</t>
+          <t>output\100_popular_cars_in_India_86_Honda_Accord\Honda_Accord.mp4</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_90_Volkswagen_Vento\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:48:25</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor Plus</t>
+          <t>Honda Accord</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
+          <t>output\100_popular_cars_in_India_86_Honda_Accord\Honda_Accord.mp4</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -7398,27 +7398,27 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor Plus</t>
+          <t>Volkswagen Virtus</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
+          <t>output\100_popular_cars_in_India_87_Volkswagen_Virtus\Volkswagen_Virtus.mp4</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -7438,27 +7438,27 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Yamaha RX100</t>
+          <t>Volkswagen Virtus</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
+          <t>output\100_popular_cars_in_India_87_Volkswagen_Virtus\Volkswagen_Virtus.mp4</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -7478,27 +7478,27 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Yamaha RX100</t>
+          <t>Volkswagen Taigun</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
+          <t>output\100_popular_cars_in_India_88_Volkswagen_Taigun\Volkswagen_Taigun.mp4</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -7518,27 +7518,27 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja H2R</t>
+          <t>Volkswagen Taigun</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
+          <t>output\100_popular_cars_in_India_88_Volkswagen_Taigun\Volkswagen_Taigun.mp4</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -7558,27 +7558,27 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja H2R</t>
+          <t>Volkswagen Polo</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
+          <t>output\100_popular_cars_in_India_89_Volkswagen_Polo\Volkswagen_Polo.mp4</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -7598,17 +7598,17 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Porsche 911 GT3 RS</t>
+          <t>Volkswagen Polo</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
+          <t>output\100_popular_cars_in_India_89_Volkswagen_Polo\Volkswagen_Polo.mp4</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -7638,17 +7638,17 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Porsche 911 GT3 RS</t>
+          <t>Volkswagen Vento</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
+          <t>output\100_popular_cars_in_India_90_Volkswagen_Vento\Volkswagen_Vento.mp4</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -7678,17 +7678,17 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Ford Mustang 1969 Boss 429</t>
+          <t>Volkswagen Vento</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
+          <t>output\100_popular_cars_in_India_90_Volkswagen_Vento\Volkswagen_Vento.mp4</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -7718,17 +7718,17 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Ford Mustang 1969 Boss 429</t>
+          <t>Skoda Slavia</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
+          <t>output\100_popular_cars_in_India_91_Skoda_Slavia\Skoda_Slavia.mp4</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Nissan Skyline GT-R R34 V-Spec II</t>
+          <t>Skoda Slavia</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
+          <t>output\100_popular_cars_in_India_91_Skoda_Slavia\Skoda_Slavia.mp4</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
@@ -7798,17 +7798,17 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Nissan Skyline GT-R R34 V-Spec II</t>
+          <t>Skoda Kushaq</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
+          <t>output\100_popular_cars_in_India_92_Skoda_Kushaq\Skoda_Kushaq.mp4</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -7838,17 +7838,17 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Aventador SVJ</t>
+          <t>Skoda Kushaq</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
+          <t>output\100_popular_cars_in_India_92_Skoda_Kushaq\Skoda_Kushaq.mp4</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -7878,17 +7878,17 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Aventador SVJ</t>
+          <t>Skoda Kodiaq</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
+          <t>output\100_popular_cars_in_India_93_Skoda_Kodiaq\Skoda_Kodiaq.mp4</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -7918,27 +7918,27 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Ducati Panigale V4 S</t>
+          <t>Skoda Kodiaq</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
+          <t>output\100_popular_cars_in_India_93_Skoda_Kodiaq\Skoda_Kodiaq.mp4</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -7958,27 +7958,27 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Ducati Panigale V4 S</t>
+          <t>Skoda Superb</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
@@ -7988,27 +7988,27 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
+          <t>output\100_popular_cars_in_India_94_Skoda_Superb\Skoda_Superb.mp4</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>youtube-automation\output\100_popular_cars_in_India_94_Skoda_Superb\video.mp4</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:47:04</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Rolls Royce Phantom VIII</t>
+          <t>Skoda Superb</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
+          <t>output\100_popular_cars_in_India_94_Skoda_Superb\Skoda_Superb.mp4</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -8038,17 +8038,17 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Rolls Royce Phantom VIII</t>
+          <t>MG Hector</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
@@ -8068,27 +8068,27 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
+          <t>output\100_popular_cars_in_India_95_MG_Hector\MG_Hector.mp4</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>youtube-automation\output\100_popular_cars_in_India_95_MG_Hector\video.mp4</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:32</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>BMW S1000RR M Package</t>
+          <t>Hero Splendor Plus</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
+          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -8118,17 +8118,17 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>BMW S1000RR M Package</t>
+          <t>Hero Splendor Plus</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
+          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Toyota Supra MK4 Turbo (A80)</t>
+          <t>Yamaha RX100</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
+          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
@@ -8198,22 +8198,22 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Toyota Supra MK4 Turbo (A80)</t>
+          <t>Yamaha RX100</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
+          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -8238,17 +8238,17 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Hayabusa GSX1300R</t>
+          <t>Kawasaki Ninja H2R</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
+          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Hayabusa GSX1300R</t>
+          <t>Kawasaki Ninja H2R</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
+          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -8318,17 +8318,17 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Ferrari F40</t>
+          <t>Porsche 911 GT3 RS</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
+          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -8358,17 +8358,17 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Ferrari F40</t>
+          <t>Porsche 911 GT3 RS</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
+          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -8398,22 +8398,22 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Fat Boy 114</t>
+          <t>Ford Mustang 1969 Boss 429</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
+          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -8438,22 +8438,22 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Fat Boy 114</t>
+          <t>Ford Mustang 1969 Boss 429</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
+          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -8478,17 +8478,17 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>McLaren P1</t>
+          <t>Nissan Skyline GT-R R34 V-Spec II</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
+          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -8518,17 +8518,17 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>McLaren P1</t>
+          <t>Nissan Skyline GT-R R34 V-Spec II</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
+          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -8558,22 +8558,22 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>KTM 390 Duke</t>
+          <t>Lamborghini Aventador SVJ</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
+          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -8598,22 +8598,22 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>KTM 390 Duke</t>
+          <t>Lamborghini Aventador SVJ</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
+          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -8638,22 +8638,22 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Dodge Challenger SRT Demon 170</t>
+          <t>Ducati Panigale V4 S</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
+          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -8678,22 +8678,22 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Dodge Challenger SRT Demon 170</t>
+          <t>Ducati Panigale V4 S</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
+          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -8718,22 +8718,22 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>Yamaha YZF-R1M</t>
+          <t>Rolls Royce Phantom VIII</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
+          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -8758,22 +8758,22 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Yamaha YZF-R1M</t>
+          <t>Rolls Royce Phantom VIII</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
+          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -8798,22 +8798,22 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Mercedes-AMG G63 Brabus 800</t>
+          <t>BMW S1000RR M Package</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
+          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -8838,22 +8838,22 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Mercedes-AMG G63 Brabus 800</t>
+          <t>BMW S1000RR M Package</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
+          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -8878,17 +8878,17 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Bugatti Chiron Super Sport 300+</t>
+          <t>Toyota Supra MK4 Turbo (A80)</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
+          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -8918,17 +8918,17 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Bugatti Chiron Super Sport 300+</t>
+          <t>Toyota Supra MK4 Turbo (A80)</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
+          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -8958,17 +8958,17 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja ZX-10R</t>
+          <t>Suzuki Hayabusa GSX1300R</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
+          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -8998,17 +8998,17 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja ZX-10R</t>
+          <t>Suzuki Hayabusa GSX1300R</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
+          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -9038,22 +9038,22 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>Triumph Rocket 3 R</t>
+          <t>Ferrari F40</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
+          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -9078,22 +9078,22 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>Triumph Rocket 3 R</t>
+          <t>Ferrari F40</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
+          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -9118,22 +9118,22 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Huracan STO</t>
+          <t>Harley-Davidson Fat Boy 114</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
+          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -9158,22 +9158,22 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Huracan STO</t>
+          <t>Harley-Davidson Fat Boy 114</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
+          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -9198,22 +9198,22 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>MV Agusta Superveloce 800</t>
+          <t>McLaren P1</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
+          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -9238,22 +9238,22 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>MV Agusta Superveloce 800</t>
+          <t>McLaren P1</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
+          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -9278,22 +9278,22 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>Pagani Huayra BC</t>
+          <t>KTM 390 Duke</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
+          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -9318,22 +9318,22 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Pagani Huayra BC</t>
+          <t>KTM 390 Duke</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
+          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -9358,22 +9358,22 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>Aprilia RSV4 Factory 1100</t>
+          <t>Dodge Challenger SRT Demon 170</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
+          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -9398,22 +9398,22 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Aprilia RSV4 Factory 1100</t>
+          <t>Dodge Challenger SRT Demon 170</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
+          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -9438,22 +9438,22 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>Chevrolet Corvette Z06 (C8)</t>
+          <t>Yamaha YZF-R1M</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
+          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -9478,22 +9478,22 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Chevrolet Corvette Z06 (C8)</t>
+          <t>Yamaha YZF-R1M</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
+          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -9518,22 +9518,22 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>Honda CBR1000RR-R Fireblade SP</t>
+          <t>Mercedes-AMG G63 Brabus 800</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
+          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -9558,22 +9558,22 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>Honda CBR1000RR-R Fireblade SP</t>
+          <t>Mercedes-AMG G63 Brabus 800</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
+          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -9598,17 +9598,17 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>Nissan GT-R Nismo (R35)</t>
+          <t>Bugatti Chiron Super Sport 300+</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
+          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -9638,17 +9638,17 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>Nissan GT-R Nismo (R35)</t>
+          <t>Bugatti Chiron Super Sport 300+</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
+          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -9678,17 +9678,17 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>BMW M1000RR</t>
+          <t>Kawasaki Ninja ZX-10R</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
+          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -9718,17 +9718,17 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>BMW M1000RR</t>
+          <t>Kawasaki Ninja ZX-10R</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
+          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -9758,22 +9758,22 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>Ferrari LaFerrari</t>
+          <t>Triumph Rocket 3 R</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
+          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -9798,22 +9798,22 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Ferrari LaFerrari</t>
+          <t>Triumph Rocket 3 R</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
+          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -9838,22 +9838,22 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>KTM 1290 Super Duke R Evo</t>
+          <t>Lamborghini Huracan STO</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
+          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>KTM 1290 Super Duke R Evo</t>
+          <t>Lamborghini Huracan STO</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
+          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -9918,22 +9918,22 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>Porsche 918 Spyder</t>
+          <t>MV Agusta Superveloce 800</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
+          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -9958,22 +9958,22 @@
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Porsche 918 Spyder</t>
+          <t>MV Agusta Superveloce 800</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
+          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -9998,22 +9998,22 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Sportster S</t>
+          <t>Pagani Huayra BC</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
+          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -10038,22 +10038,22 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Sportster S</t>
+          <t>Pagani Huayra BC</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
+          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -10078,22 +10078,22 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>Shelby Cobra 427 S/C</t>
+          <t>Aprilia RSV4 Factory 1100</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
+          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -10118,22 +10118,22 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Shelby Cobra 427 S/C</t>
+          <t>Aprilia RSV4 Factory 1100</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
+          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -10158,22 +10158,22 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>Ducati Diavel V4</t>
+          <t>Chevrolet Corvette Z06 (C8)</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
+          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -10198,22 +10198,22 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Ducati Diavel V4</t>
+          <t>Chevrolet Corvette Z06 (C8)</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
+          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -10238,22 +10238,22 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Audi R8 V10 Performance</t>
+          <t>Honda CBR1000RR-R Fireblade SP</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
+          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -10278,22 +10278,22 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Audi R8 V10 Performance</t>
+          <t>Honda CBR1000RR-R Fireblade SP</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
+          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -10318,22 +10318,22 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-10 SP</t>
+          <t>Nissan GT-R Nismo (R35)</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
+          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -10358,22 +10358,22 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-10 SP</t>
+          <t>Nissan GT-R Nismo (R35)</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
+          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -10398,22 +10398,22 @@
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>Mazda RX-7 Spirit R (FD3S)</t>
+          <t>BMW M1000RR</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
+          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -10438,22 +10438,22 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>Mazda RX-7 Spirit R (FD3S)</t>
+          <t>BMW M1000RR</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
+          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -10478,22 +10478,22 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z H2 Supercharged</t>
+          <t>Ferrari LaFerrari</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
+          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -10518,22 +10518,22 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z H2 Supercharged</t>
+          <t>Ferrari LaFerrari</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
+          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -10558,22 +10558,22 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>Lexus LFA Nurburgring Edition</t>
+          <t>KTM 1290 Super Duke R Evo</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -10598,22 +10598,22 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>Lexus LFA Nurburgring Edition</t>
+          <t>KTM 1290 Super Duke R Evo</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -10638,22 +10638,22 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Katana</t>
+          <t>Porsche 918 Spyder</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -10678,22 +10678,22 @@
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Katana</t>
+          <t>Porsche 918 Spyder</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -10718,22 +10718,22 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>McLaren 720S Spider</t>
+          <t>Harley-Davidson Sportster S</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -10758,22 +10758,22 @@
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>McLaren 720S Spider</t>
+          <t>Harley-Davidson Sportster S</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -10798,22 +10798,22 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>Honda CB1000R Black Edition</t>
+          <t>Shelby Cobra 427 S/C</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -10838,22 +10838,22 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Honda CB1000R Black Edition</t>
+          <t>Shelby Cobra 427 S/C</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -10878,22 +10878,22 @@
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Murcielago LP670-4 SV</t>
+          <t>Ducati Diavel V4</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -10918,22 +10918,22 @@
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Murcielago LP670-4 SV</t>
+          <t>Ducati Diavel V4</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -10958,22 +10958,22 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 22:47:11</t>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>Indian Scout Bobber</t>
+          <t>Audi R8 V10 Performance</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
+          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -10998,47 +10998,767 @@
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 17:35:41</t>
+          <t>2026-09-19 03:46:50</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>Audi R8 V10 Performance</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E264" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:51:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT-10 SP</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E265" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:46:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>Yamaha MT-10 SP</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E266" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:51:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>Mazda RX-7 Spirit R (FD3S)</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E267" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:46:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>Mazda RX-7 Spirit R (FD3S)</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E268" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:51:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z H2 Supercharged</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E269" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:46:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>Kawasaki Z H2 Supercharged</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E270" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:51:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>Lexus LFA Nurburgring Edition</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E271" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:46:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>Lexus LFA Nurburgring Edition</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E272" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:51:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>Suzuki Katana</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E273" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+        </is>
+      </c>
+      <c r="G273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:46:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>Suzuki Katana</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E274" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:51:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>McLaren 720S Spider</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E275" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:46:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>McLaren 720S Spider</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E276" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:51:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB1000R Black Edition</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E277" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:46:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB1000R Black Edition</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E278" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:51:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>Lamborghini Murcielago LP670-4 SV</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E279" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+        </is>
+      </c>
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:46:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>Lamborghini Murcielago LP670-4 SV</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E280" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:51:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B264" s="3" t="inlineStr">
+      <c r="B281" s="3" t="inlineStr">
         <is>
           <t>Indian Scout Bobber</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
+      <c r="C281" s="2" t="inlineStr">
         <is>
           <t>Motorcycle</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="D281" s="2" t="inlineStr">
         <is>
           <t>master_vehicles_tracker</t>
         </is>
       </c>
-      <c r="E264" s="4" t="inlineStr">
-        <is>
-          <t>EDITED</t>
-        </is>
-      </c>
-      <c r="F264" s="3" t="inlineStr">
+      <c r="E281" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
         <is>
           <t>output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
         </is>
       </c>
-      <c r="G264" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H264" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16 22:47:11</t>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:46:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>Indian Scout Bobber</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E282" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 03:51:23</t>
         </is>
       </c>
     </row>

--- a/video-editor/editor_tracker.xlsx
+++ b/video-editor/editor_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H282"/>
+  <dimension ref="A1:H288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="109" customWidth="1" min="6" max="6"/>
-    <col width="81" customWidth="1" min="7" max="7"/>
+    <col width="93" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -558,7 +558,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -7993,12 +7993,12 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_94_Skoda_Superb\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:47:04</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
@@ -8073,32 +8073,32 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_95_MG_Hector\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:32</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor Plus</t>
+          <t>MG Hector</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
+          <t>output\100_popular_cars_in_India_95_MG_Hector\MG_Hector.mp4</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -8118,27 +8118,27 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor Plus</t>
+          <t>MG Astor</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
+          <t>output\100_popular_cars_in_India_96_MG_Astor\MG_Astor.mp4</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -8158,27 +8158,27 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Yamaha RX100</t>
+          <t>MG Astor</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
+          <t>output\100_popular_cars_in_India_96_MG_Astor\MG_Astor.mp4</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
@@ -8198,27 +8198,27 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Yamaha RX100</t>
+          <t>Mahindra Scorpio Classic</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
@@ -8228,37 +8228,37 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
+          <t>output\100_popular_cars_in_India_97_Mahindra_Scorpio_Classic\Mahindra_Scorpio_Classic.mp4</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>youtube-automation\output\100_popular_cars_in_India_97_Mahindra_Scorpio_Classic\video.mp4</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 00:56:55</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja H2R</t>
+          <t>Mahindra Scorpio Classic</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
+          <t>output\100_popular_cars_in_India_97_Mahindra_Scorpio_Classic\Mahindra_Scorpio_Classic.mp4</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -8278,27 +8278,27 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja H2R</t>
+          <t>Hyundai Grand i10 Nios</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
@@ -8308,32 +8308,32 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
+          <t>output\100_popular_cars_in_India_98_Hyundai_Grand_i10_Nios\Hyundai_Grand_i10_Nios.mp4</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>youtube-automation\output\100_popular_cars_in_India_98_Hyundai_Grand_i10_Nios\video.mp4</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:39</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Porsche 911 GT3 RS</t>
+          <t>Hero Splendor Plus</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
+          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -8358,22 +8358,22 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Porsche 911 GT3 RS</t>
+          <t>Hero Splendor Plus</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
+          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -8398,22 +8398,22 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Ford Mustang 1969 Boss 429</t>
+          <t>Yamaha RX100</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
+          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -8438,22 +8438,22 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Ford Mustang 1969 Boss 429</t>
+          <t>Yamaha RX100</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
+          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -8478,22 +8478,22 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Nissan Skyline GT-R R34 V-Spec II</t>
+          <t>Kawasaki Ninja H2R</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
+          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -8518,22 +8518,22 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Nissan Skyline GT-R R34 V-Spec II</t>
+          <t>Kawasaki Ninja H2R</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
+          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -8558,17 +8558,17 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Aventador SVJ</t>
+          <t>Porsche 911 GT3 RS</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
+          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -8598,17 +8598,17 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Aventador SVJ</t>
+          <t>Porsche 911 GT3 RS</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
+          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -8638,22 +8638,22 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Ducati Panigale V4 S</t>
+          <t>Ford Mustang 1969 Boss 429</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
+          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -8678,22 +8678,22 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Ducati Panigale V4 S</t>
+          <t>Ford Mustang 1969 Boss 429</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
+          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -8718,17 +8718,17 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>Rolls Royce Phantom VIII</t>
+          <t>Nissan Skyline GT-R R34 V-Spec II</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
+          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -8758,17 +8758,17 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Rolls Royce Phantom VIII</t>
+          <t>Nissan Skyline GT-R R34 V-Spec II</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
+          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -8798,22 +8798,22 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>BMW S1000RR M Package</t>
+          <t>Lamborghini Aventador SVJ</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
+          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -8838,22 +8838,22 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>BMW S1000RR M Package</t>
+          <t>Lamborghini Aventador SVJ</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
+          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -8878,22 +8878,22 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Toyota Supra MK4 Turbo (A80)</t>
+          <t>Ducati Panigale V4 S</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
+          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -8918,22 +8918,22 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Toyota Supra MK4 Turbo (A80)</t>
+          <t>Ducati Panigale V4 S</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
+          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -8958,22 +8958,22 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Hayabusa GSX1300R</t>
+          <t>Rolls Royce Phantom VIII</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
+          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -8998,22 +8998,22 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Hayabusa GSX1300R</t>
+          <t>Rolls Royce Phantom VIII</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
+          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -9038,22 +9038,22 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>Ferrari F40</t>
+          <t>BMW S1000RR M Package</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
+          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -9078,22 +9078,22 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>Ferrari F40</t>
+          <t>BMW S1000RR M Package</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
+          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -9118,22 +9118,22 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Fat Boy 114</t>
+          <t>Toyota Supra MK4 Turbo (A80)</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
+          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -9158,22 +9158,22 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Fat Boy 114</t>
+          <t>Toyota Supra MK4 Turbo (A80)</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
+          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -9198,22 +9198,22 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>McLaren P1</t>
+          <t>Suzuki Hayabusa GSX1300R</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
+          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -9238,22 +9238,22 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>McLaren P1</t>
+          <t>Suzuki Hayabusa GSX1300R</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
+          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -9278,22 +9278,22 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>KTM 390 Duke</t>
+          <t>Ferrari F40</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
+          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -9318,22 +9318,22 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>KTM 390 Duke</t>
+          <t>Ferrari F40</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
+          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -9358,22 +9358,22 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>Dodge Challenger SRT Demon 170</t>
+          <t>Harley-Davidson Fat Boy 114</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
+          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -9398,22 +9398,22 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Dodge Challenger SRT Demon 170</t>
+          <t>Harley-Davidson Fat Boy 114</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
+          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -9438,22 +9438,22 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>Yamaha YZF-R1M</t>
+          <t>McLaren P1</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
+          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -9478,22 +9478,22 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Yamaha YZF-R1M</t>
+          <t>McLaren P1</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
+          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -9518,22 +9518,22 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>Mercedes-AMG G63 Brabus 800</t>
+          <t>KTM 390 Duke</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
+          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -9558,22 +9558,22 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>Mercedes-AMG G63 Brabus 800</t>
+          <t>KTM 390 Duke</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
+          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -9598,17 +9598,17 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>Bugatti Chiron Super Sport 300+</t>
+          <t>Dodge Challenger SRT Demon 170</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
+          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -9638,17 +9638,17 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>Bugatti Chiron Super Sport 300+</t>
+          <t>Dodge Challenger SRT Demon 170</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
+          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -9678,17 +9678,17 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja ZX-10R</t>
+          <t>Yamaha YZF-R1M</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
+          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -9718,17 +9718,17 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja ZX-10R</t>
+          <t>Yamaha YZF-R1M</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
+          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -9758,22 +9758,22 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>Triumph Rocket 3 R</t>
+          <t>Mercedes-AMG G63 Brabus 800</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
+          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -9798,22 +9798,22 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Triumph Rocket 3 R</t>
+          <t>Mercedes-AMG G63 Brabus 800</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
+          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -9838,17 +9838,17 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Huracan STO</t>
+          <t>Bugatti Chiron Super Sport 300+</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
+          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -9878,17 +9878,17 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Huracan STO</t>
+          <t>Bugatti Chiron Super Sport 300+</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
+          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -9918,17 +9918,17 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>MV Agusta Superveloce 800</t>
+          <t>Kawasaki Ninja ZX-10R</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
+          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>MV Agusta Superveloce 800</t>
+          <t>Kawasaki Ninja ZX-10R</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
+          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -9998,22 +9998,22 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>Pagani Huayra BC</t>
+          <t>Triumph Rocket 3 R</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
+          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -10038,22 +10038,22 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Pagani Huayra BC</t>
+          <t>Triumph Rocket 3 R</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
+          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -10078,22 +10078,22 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>Aprilia RSV4 Factory 1100</t>
+          <t>Lamborghini Huracan STO</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
+          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -10118,22 +10118,22 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Aprilia RSV4 Factory 1100</t>
+          <t>Lamborghini Huracan STO</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
+          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -10158,22 +10158,22 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>Chevrolet Corvette Z06 (C8)</t>
+          <t>MV Agusta Superveloce 800</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
+          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -10198,22 +10198,22 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Chevrolet Corvette Z06 (C8)</t>
+          <t>MV Agusta Superveloce 800</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
+          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -10238,22 +10238,22 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Honda CBR1000RR-R Fireblade SP</t>
+          <t>Pagani Huayra BC</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
+          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -10278,22 +10278,22 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Honda CBR1000RR-R Fireblade SP</t>
+          <t>Pagani Huayra BC</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
+          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -10318,22 +10318,22 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Nissan GT-R Nismo (R35)</t>
+          <t>Aprilia RSV4 Factory 1100</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
+          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -10358,22 +10358,22 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>Nissan GT-R Nismo (R35)</t>
+          <t>Aprilia RSV4 Factory 1100</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
+          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -10398,22 +10398,22 @@
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>BMW M1000RR</t>
+          <t>Chevrolet Corvette Z06 (C8)</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
+          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -10438,22 +10438,22 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>BMW M1000RR</t>
+          <t>Chevrolet Corvette Z06 (C8)</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
+          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -10478,22 +10478,22 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>Ferrari LaFerrari</t>
+          <t>Honda CBR1000RR-R Fireblade SP</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
+          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -10518,22 +10518,22 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Ferrari LaFerrari</t>
+          <t>Honda CBR1000RR-R Fireblade SP</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
+          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -10558,22 +10558,22 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>KTM 1290 Super Duke R Evo</t>
+          <t>Nissan GT-R Nismo (R35)</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
+          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -10598,22 +10598,22 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>KTM 1290 Super Duke R Evo</t>
+          <t>Nissan GT-R Nismo (R35)</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
+          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -10638,22 +10638,22 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>Porsche 918 Spyder</t>
+          <t>BMW M1000RR</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
+          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -10678,22 +10678,22 @@
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Porsche 918 Spyder</t>
+          <t>BMW M1000RR</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
+          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -10718,22 +10718,22 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Sportster S</t>
+          <t>Ferrari LaFerrari</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
+          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -10758,22 +10758,22 @@
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Sportster S</t>
+          <t>Ferrari LaFerrari</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
+          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -10798,22 +10798,22 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>Shelby Cobra 427 S/C</t>
+          <t>KTM 1290 Super Duke R Evo</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
+          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -10838,22 +10838,22 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Shelby Cobra 427 S/C</t>
+          <t>KTM 1290 Super Duke R Evo</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
+          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -10878,22 +10878,22 @@
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>Ducati Diavel V4</t>
+          <t>Porsche 918 Spyder</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
+          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -10918,22 +10918,22 @@
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Ducati Diavel V4</t>
+          <t>Porsche 918 Spyder</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
+          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -10958,22 +10958,22 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>Audi R8 V10 Performance</t>
+          <t>Harley-Davidson Sportster S</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
+          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -10998,22 +10998,22 @@
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>Audi R8 V10 Performance</t>
+          <t>Harley-Davidson Sportster S</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
+          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -11038,22 +11038,22 @@
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-10 SP</t>
+          <t>Shelby Cobra 427 S/C</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
+          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -11078,22 +11078,22 @@
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-10 SP</t>
+          <t>Shelby Cobra 427 S/C</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
+          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -11118,22 +11118,22 @@
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>Mazda RX-7 Spirit R (FD3S)</t>
+          <t>Ducati Diavel V4</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
+          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -11158,22 +11158,22 @@
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Mazda RX-7 Spirit R (FD3S)</t>
+          <t>Ducati Diavel V4</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
+          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z H2 Supercharged</t>
+          <t>Audi R8 V10 Performance</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
+          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -11238,22 +11238,22 @@
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z H2 Supercharged</t>
+          <t>Audi R8 V10 Performance</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
+          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -11278,22 +11278,22 @@
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>Lexus LFA Nurburgring Edition</t>
+          <t>Yamaha MT-10 SP</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -11318,22 +11318,22 @@
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Lexus LFA Nurburgring Edition</t>
+          <t>Yamaha MT-10 SP</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -11358,22 +11358,22 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Katana</t>
+          <t>Mazda RX-7 Spirit R (FD3S)</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -11398,22 +11398,22 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Katana</t>
+          <t>Mazda RX-7 Spirit R (FD3S)</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -11438,22 +11438,22 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>McLaren 720S Spider</t>
+          <t>Kawasaki Z H2 Supercharged</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -11478,22 +11478,22 @@
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>McLaren 720S Spider</t>
+          <t>Kawasaki Z H2 Supercharged</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -11518,22 +11518,22 @@
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>Honda CB1000R Black Edition</t>
+          <t>Lexus LFA Nurburgring Edition</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -11558,22 +11558,22 @@
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Honda CB1000R Black Edition</t>
+          <t>Lexus LFA Nurburgring Edition</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Murcielago LP670-4 SV</t>
+          <t>Suzuki Katana</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -11638,22 +11638,22 @@
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Murcielago LP670-4 SV</t>
+          <t>Suzuki Katana</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -11678,22 +11678,22 @@
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:51:23</t>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>Indian Scout Bobber</t>
+          <t>McLaren 720S Spider</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
+          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -11718,47 +11718,287 @@
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 03:46:50</t>
+          <t>2026-09-20 00:56:48</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>McLaren 720S Spider</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E282" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 01:00:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB1000R Black Edition</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E283" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+        </is>
+      </c>
+      <c r="G283" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:56:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB1000R Black Edition</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E284" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 01:00:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>Lamborghini Murcielago LP670-4 SV</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E285" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:56:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>Lamborghini Murcielago LP670-4 SV</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E286" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 01:00:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B282" s="3" t="inlineStr">
+      <c r="B287" s="3" t="inlineStr">
         <is>
           <t>Indian Scout Bobber</t>
         </is>
       </c>
-      <c r="C282" s="2" t="inlineStr">
+      <c r="C287" s="2" t="inlineStr">
         <is>
           <t>Motorcycle</t>
         </is>
       </c>
-      <c r="D282" s="2" t="inlineStr">
+      <c r="D287" s="2" t="inlineStr">
         <is>
           <t>master_vehicles_tracker</t>
         </is>
       </c>
-      <c r="E282" s="4" t="inlineStr">
-        <is>
-          <t>EDITED</t>
-        </is>
-      </c>
-      <c r="F282" s="3" t="inlineStr">
+      <c r="E287" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="inlineStr">
         <is>
           <t>output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
         </is>
       </c>
-      <c r="G282" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H282" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-19 03:51:23</t>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 00:56:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>Indian Scout Bobber</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E288" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 01:00:32</t>
         </is>
       </c>
     </row>

--- a/video-editor/editor_tracker.xlsx
+++ b/video-editor/editor_tracker.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H288"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="109" customWidth="1" min="6" max="6"/>
-    <col width="93" customWidth="1" min="7" max="7"/>
+    <col width="82" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -558,7 +558,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -8233,12 +8233,12 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_97_Mahindra_Scorpio_Classic\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:55</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -8313,32 +8313,32 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_98_Hyundai_Grand_i10_Nios\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:39</t>
+          <t>2026-09-21 00:12:28</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor Plus</t>
+          <t>Hyundai Grand i10 Nios</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
+          <t>output\100_popular_cars_in_India_98_Hyundai_Grand_i10_Nios\Hyundai_Grand_i10_Nios.mp4</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -8358,27 +8358,27 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor Plus</t>
+          <t>MG ZS EV</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
@@ -8388,37 +8388,37 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
+          <t>output\100_popular_cars_in_India_99_MG_ZS_EV\MG_ZS_EV.mp4</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>youtube-automation\output\100_popular_cars_in_India_99_MG_ZS_EV\video.mp4</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:12:47</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Yamaha RX100</t>
+          <t>MG ZS EV</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
+          <t>output\100_popular_cars_in_India_99_MG_ZS_EV\MG_ZS_EV.mp4</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -8438,27 +8438,27 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Yamaha RX100</t>
+          <t>Jeep Compass</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
@@ -8468,27 +8468,27 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
+          <t>output\100_popular_cars_in_India_100_Jeep_Compass\Jeep_Compass.mp4</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>youtube-automation\output\100_popular_cars_in_India_100_Jeep_Compass\video.mp4</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:23</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja H2R</t>
+          <t>Hero Splendor Plus</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
+          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -8518,17 +8518,17 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja H2R</t>
+          <t>Hero Splendor Plus</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
+          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -8558,22 +8558,22 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Porsche 911 GT3 RS</t>
+          <t>Yamaha RX100</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
+          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -8598,22 +8598,22 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Porsche 911 GT3 RS</t>
+          <t>Yamaha RX100</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
+          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -8638,22 +8638,22 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Ford Mustang 1969 Boss 429</t>
+          <t>Kawasaki Ninja H2R</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
+          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -8678,22 +8678,22 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Ford Mustang 1969 Boss 429</t>
+          <t>Kawasaki Ninja H2R</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
+          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -8718,17 +8718,17 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>Nissan Skyline GT-R R34 V-Spec II</t>
+          <t>Porsche 911 GT3 RS</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
+          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -8758,17 +8758,17 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Nissan Skyline GT-R R34 V-Spec II</t>
+          <t>Porsche 911 GT3 RS</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
+          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -8798,17 +8798,17 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Aventador SVJ</t>
+          <t>Ford Mustang 1969 Boss 429</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
+          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -8838,17 +8838,17 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Aventador SVJ</t>
+          <t>Ford Mustang 1969 Boss 429</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
+          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -8878,22 +8878,22 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Ducati Panigale V4 S</t>
+          <t>Nissan Skyline GT-R R34 V-Spec II</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
+          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -8918,22 +8918,22 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Ducati Panigale V4 S</t>
+          <t>Nissan Skyline GT-R R34 V-Spec II</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
+          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -8958,17 +8958,17 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>Rolls Royce Phantom VIII</t>
+          <t>Lamborghini Aventador SVJ</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
+          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -8998,17 +8998,17 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Rolls Royce Phantom VIII</t>
+          <t>Lamborghini Aventador SVJ</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
+          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -9038,17 +9038,17 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>BMW S1000RR M Package</t>
+          <t>Ducati Panigale V4 S</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
+          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>BMW S1000RR M Package</t>
+          <t>Ducati Panigale V4 S</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
+          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -9118,17 +9118,17 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>Toyota Supra MK4 Turbo (A80)</t>
+          <t>Rolls Royce Phantom VIII</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
+          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -9158,17 +9158,17 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Toyota Supra MK4 Turbo (A80)</t>
+          <t>Rolls Royce Phantom VIII</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
+          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -9198,17 +9198,17 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Hayabusa GSX1300R</t>
+          <t>BMW S1000RR M Package</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
+          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -9238,17 +9238,17 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Hayabusa GSX1300R</t>
+          <t>BMW S1000RR M Package</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
+          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -9278,17 +9278,17 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>Ferrari F40</t>
+          <t>Toyota Supra MK4 Turbo (A80)</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
+          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -9318,17 +9318,17 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Ferrari F40</t>
+          <t>Toyota Supra MK4 Turbo (A80)</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
+          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Fat Boy 114</t>
+          <t>Suzuki Hayabusa GSX1300R</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
+          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -9398,17 +9398,17 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Fat Boy 114</t>
+          <t>Suzuki Hayabusa GSX1300R</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
+          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -9438,17 +9438,17 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>McLaren P1</t>
+          <t>Ferrari F40</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
+          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -9478,17 +9478,17 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>McLaren P1</t>
+          <t>Ferrari F40</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
+          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -9518,17 +9518,17 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>KTM 390 Duke</t>
+          <t>Harley-Davidson Fat Boy 114</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
+          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -9558,17 +9558,17 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>KTM 390 Duke</t>
+          <t>Harley-Davidson Fat Boy 114</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
+          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -9598,17 +9598,17 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>Dodge Challenger SRT Demon 170</t>
+          <t>McLaren P1</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
+          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -9638,17 +9638,17 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>Dodge Challenger SRT Demon 170</t>
+          <t>McLaren P1</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
+          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -9678,17 +9678,17 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>Yamaha YZF-R1M</t>
+          <t>KTM 390 Duke</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
+          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -9718,17 +9718,17 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Yamaha YZF-R1M</t>
+          <t>KTM 390 Duke</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
+          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -9758,17 +9758,17 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>Mercedes-AMG G63 Brabus 800</t>
+          <t>Dodge Challenger SRT Demon 170</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
+          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -9798,17 +9798,17 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Mercedes-AMG G63 Brabus 800</t>
+          <t>Dodge Challenger SRT Demon 170</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
+          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -9838,22 +9838,22 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>Bugatti Chiron Super Sport 300+</t>
+          <t>Yamaha YZF-R1M</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
+          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Bugatti Chiron Super Sport 300+</t>
+          <t>Yamaha YZF-R1M</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
+          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -9918,22 +9918,22 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja ZX-10R</t>
+          <t>Mercedes-AMG G63 Brabus 800</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
+          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -9958,22 +9958,22 @@
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja ZX-10R</t>
+          <t>Mercedes-AMG G63 Brabus 800</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
+          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -9998,22 +9998,22 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>Triumph Rocket 3 R</t>
+          <t>Bugatti Chiron Super Sport 300+</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
+          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -10038,22 +10038,22 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Triumph Rocket 3 R</t>
+          <t>Bugatti Chiron Super Sport 300+</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
+          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -10078,22 +10078,22 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Huracan STO</t>
+          <t>Kawasaki Ninja ZX-10R</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
+          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -10118,22 +10118,22 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Huracan STO</t>
+          <t>Kawasaki Ninja ZX-10R</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
+          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -10158,17 +10158,17 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>MV Agusta Superveloce 800</t>
+          <t>Triumph Rocket 3 R</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
+          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -10198,17 +10198,17 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>MV Agusta Superveloce 800</t>
+          <t>Triumph Rocket 3 R</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
+          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -10238,17 +10238,17 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Pagani Huayra BC</t>
+          <t>Lamborghini Huracan STO</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
+          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -10278,17 +10278,17 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Pagani Huayra BC</t>
+          <t>Lamborghini Huracan STO</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
+          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -10318,17 +10318,17 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Aprilia RSV4 Factory 1100</t>
+          <t>MV Agusta Superveloce 800</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
+          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -10358,17 +10358,17 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>Aprilia RSV4 Factory 1100</t>
+          <t>MV Agusta Superveloce 800</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
+          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -10398,17 +10398,17 @@
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>Chevrolet Corvette Z06 (C8)</t>
+          <t>Pagani Huayra BC</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
+          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -10438,17 +10438,17 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>Chevrolet Corvette Z06 (C8)</t>
+          <t>Pagani Huayra BC</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
+          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>Honda CBR1000RR-R Fireblade SP</t>
+          <t>Aprilia RSV4 Factory 1100</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
+          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -10518,17 +10518,17 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Honda CBR1000RR-R Fireblade SP</t>
+          <t>Aprilia RSV4 Factory 1100</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
+          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -10558,17 +10558,17 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>Nissan GT-R Nismo (R35)</t>
+          <t>Chevrolet Corvette Z06 (C8)</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
+          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -10598,17 +10598,17 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>Nissan GT-R Nismo (R35)</t>
+          <t>Chevrolet Corvette Z06 (C8)</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
+          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -10638,17 +10638,17 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>BMW M1000RR</t>
+          <t>Honda CBR1000RR-R Fireblade SP</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
+          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -10678,17 +10678,17 @@
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>BMW M1000RR</t>
+          <t>Honda CBR1000RR-R Fireblade SP</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
+          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -10718,17 +10718,17 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>Ferrari LaFerrari</t>
+          <t>Nissan GT-R Nismo (R35)</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
+          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -10758,17 +10758,17 @@
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:26</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>Ferrari LaFerrari</t>
+          <t>Nissan GT-R Nismo (R35)</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
+          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>KTM 1290 Super Duke R Evo</t>
+          <t>BMW M1000RR</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
+          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -10838,17 +10838,17 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>KTM 1290 Super Duke R Evo</t>
+          <t>BMW M1000RR</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
+          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -10878,17 +10878,17 @@
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>Porsche 918 Spyder</t>
+          <t>Ferrari LaFerrari</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
+          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -10918,17 +10918,17 @@
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Porsche 918 Spyder</t>
+          <t>Ferrari LaFerrari</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
+          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Sportster S</t>
+          <t>KTM 1290 Super Duke R Evo</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
+          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -10998,17 +10998,17 @@
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Sportster S</t>
+          <t>KTM 1290 Super Duke R Evo</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
+          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -11038,17 +11038,17 @@
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>Shelby Cobra 427 S/C</t>
+          <t>Porsche 918 Spyder</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
+          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -11078,17 +11078,17 @@
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Shelby Cobra 427 S/C</t>
+          <t>Porsche 918 Spyder</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
+          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -11118,17 +11118,17 @@
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>Ducati Diavel V4</t>
+          <t>Harley-Davidson Sportster S</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
+          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -11158,17 +11158,17 @@
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Ducati Diavel V4</t>
+          <t>Harley-Davidson Sportster S</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
+          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -11198,17 +11198,17 @@
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>Audi R8 V10 Performance</t>
+          <t>Shelby Cobra 427 S/C</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
+          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -11238,17 +11238,17 @@
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Audi R8 V10 Performance</t>
+          <t>Shelby Cobra 427 S/C</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
+          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -11278,17 +11278,17 @@
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-10 SP</t>
+          <t>Ducati Diavel V4</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
+          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -11318,17 +11318,17 @@
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-10 SP</t>
+          <t>Ducati Diavel V4</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
+          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -11358,17 +11358,17 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>Mazda RX-7 Spirit R (FD3S)</t>
+          <t>Audi R8 V10 Performance</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
+          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -11398,17 +11398,17 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Mazda RX-7 Spirit R (FD3S)</t>
+          <t>Audi R8 V10 Performance</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
+          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -11438,17 +11438,17 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z H2 Supercharged</t>
+          <t>Yamaha MT-10 SP</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
+          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -11478,17 +11478,17 @@
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z H2 Supercharged</t>
+          <t>Yamaha MT-10 SP</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
+          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -11518,17 +11518,17 @@
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>Lexus LFA Nurburgring Edition</t>
+          <t>Mazda RX-7 Spirit R (FD3S)</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -11558,17 +11558,17 @@
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Lexus LFA Nurburgring Edition</t>
+          <t>Mazda RX-7 Spirit R (FD3S)</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -11598,17 +11598,17 @@
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Katana</t>
+          <t>Kawasaki Z H2 Supercharged</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -11638,17 +11638,17 @@
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Katana</t>
+          <t>Kawasaki Z H2 Supercharged</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -11678,17 +11678,17 @@
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>McLaren 720S Spider</t>
+          <t>Lexus LFA Nurburgring Edition</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -11718,17 +11718,17 @@
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>McLaren 720S Spider</t>
+          <t>Lexus LFA Nurburgring Edition</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -11758,17 +11758,17 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>Honda CB1000R Black Edition</t>
+          <t>Suzuki Katana</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -11798,17 +11798,17 @@
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Honda CB1000R Black Edition</t>
+          <t>Suzuki Katana</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -11838,17 +11838,17 @@
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Murcielago LP670-4 SV</t>
+          <t>McLaren 720S Spider</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -11878,17 +11878,17 @@
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Murcielago LP670-4 SV</t>
+          <t>McLaren 720S Spider</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -11918,17 +11918,17 @@
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 01:00:32</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>Indian Scout Bobber</t>
+          <t>Honda CB1000R Black Edition</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
+          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -11958,47 +11958,207 @@
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20 00:56:48</t>
+          <t>2026-09-21 00:12:27</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB1000R Black Edition</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E288" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:29:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>Lamborghini Murcielago LP670-4 SV</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E289" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F289" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+        </is>
+      </c>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:12:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>Lamborghini Murcielago LP670-4 SV</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E290" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F290" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+        </is>
+      </c>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:29:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B288" s="3" t="inlineStr">
+      <c r="B291" s="3" t="inlineStr">
         <is>
           <t>Indian Scout Bobber</t>
         </is>
       </c>
-      <c r="C288" s="2" t="inlineStr">
+      <c r="C291" s="2" t="inlineStr">
         <is>
           <t>Motorcycle</t>
         </is>
       </c>
-      <c r="D288" s="2" t="inlineStr">
+      <c r="D291" s="2" t="inlineStr">
         <is>
           <t>master_vehicles_tracker</t>
         </is>
       </c>
-      <c r="E288" s="4" t="inlineStr">
-        <is>
-          <t>EDITED</t>
-        </is>
-      </c>
-      <c r="F288" s="3" t="inlineStr">
+      <c r="E291" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F291" s="3" t="inlineStr">
         <is>
           <t>output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
         </is>
       </c>
-      <c r="G288" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H288" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-20 01:00:32</t>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:12:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>Indian Scout Bobber</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E292" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>

--- a/video-editor/editor_tracker.xlsx
+++ b/video-editor/editor_tracker.xlsx
@@ -467,16 +467,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H292"/>
+  <dimension ref="A1:H296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="109" customWidth="1" min="6" max="6"/>
-    <col width="82" customWidth="1" min="7" max="7"/>
+    <col width="98" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -558,7 +558,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:28</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -8393,12 +8393,12 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>youtube-automation\output\100_popular_cars_in_India_99_MG_ZS_EV\video.mp4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:47</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -8484,21 +8484,21 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor Plus</t>
+          <t>Jeep Compass</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>100_popular_cars_in_India</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
+          <t>output\100_popular_cars_in_India_100_Jeep_Compass\Jeep_Compass.mp4</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
@@ -8528,17 +8528,17 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor Plus</t>
+          <t>Ford F-150</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>Popular_Cars_USA_Canada_Top_50</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
@@ -8548,17 +8548,17 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
+          <t>output\Popular_Cars_USA_Canada_Top_50_01_Ford_F-150\Ford_F-150.mp4</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>youtube-automation\output\Popular_Cars_USA_Canada_Top_50_01_Ford_F-150\video.mp4</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:50</t>
         </is>
       </c>
     </row>
@@ -8568,17 +8568,17 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Yamaha RX100</t>
+          <t>Chevrolet Silverado 1500</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>Popular_Cars_USA_Canada_Top_50</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
@@ -8588,37 +8588,37 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
+          <t>output\Popular_Cars_USA_Canada_Top_50_02_Chevrolet_Silverado_1500\Chevrolet_Silverado_1500.mp4</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>youtube-automation\output\Popular_Cars_USA_Canada_Top_50_02_Chevrolet_Silverado_1500\video.mp4</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-23 18:05:55</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Yamaha RX100</t>
+          <t>Toyota RAV4</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>master_vehicles_tracker</t>
+          <t>Popular_Cars_USA_Canada_Top_50</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
@@ -8628,27 +8628,27 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
+          <t>output\Popular_Cars_USA_Canada_Top_50_03_Toyota_RAV4\Toyota_RAV4.mp4</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>youtube-automation\output\Popular_Cars_USA_Canada_Top_50_03_Toyota_RAV4\video.mp4</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:06:01</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja H2R</t>
+          <t>Hero Splendor Plus</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
+          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -8678,17 +8678,17 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja H2R</t>
+          <t>Hero Splendor Plus</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
+          <t>output\master_vehicles_tracker_01_Hero_Splendor_Plus\Hero_Splendor_Plus.mp4</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -8718,22 +8718,22 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>Porsche 911 GT3 RS</t>
+          <t>Yamaha RX100</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
+          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -8758,22 +8758,22 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Porsche 911 GT3 RS</t>
+          <t>Yamaha RX100</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
+          <t>output\master_vehicles_tracker_02_Yamaha_RX100\Yamaha_RX100.mp4</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -8798,22 +8798,22 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Ford Mustang 1969 Boss 429</t>
+          <t>Kawasaki Ninja H2R</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
+          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -8838,22 +8838,22 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Ford Mustang 1969 Boss 429</t>
+          <t>Kawasaki Ninja H2R</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
+          <t>output\master_vehicles_tracker_04_Kawasaki_Ninja_H2R\Kawasaki_Ninja_H2R.mp4</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -8878,17 +8878,17 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Nissan Skyline GT-R R34 V-Spec II</t>
+          <t>Porsche 911 GT3 RS</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
+          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -8918,17 +8918,17 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Nissan Skyline GT-R R34 V-Spec II</t>
+          <t>Porsche 911 GT3 RS</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
+          <t>output\master_vehicles_tracker_05_Porsche_911_GT3_RS\Porsche_911_GT3_RS.mp4</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -8958,17 +8958,17 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Aventador SVJ</t>
+          <t>Ford Mustang 1969 Boss 429</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
+          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -8998,17 +8998,17 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Aventador SVJ</t>
+          <t>Ford Mustang 1969 Boss 429</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
+          <t>output\master_vehicles_tracker_06_Ford_Mustang_1969_Boss_429\Ford_Mustang_1969_Boss_429.mp4</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -9038,22 +9038,22 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>Ducati Panigale V4 S</t>
+          <t>Nissan Skyline GT-R R34 V-Spec II</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
+          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -9078,22 +9078,22 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>Ducati Panigale V4 S</t>
+          <t>Nissan Skyline GT-R R34 V-Spec II</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
+          <t>output\master_vehicles_tracker_07_Nissan_Skyline_GT-R_R34_V-Spec_II\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -9118,17 +9118,17 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>Rolls Royce Phantom VIII</t>
+          <t>Lamborghini Aventador SVJ</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
+          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -9158,17 +9158,17 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Rolls Royce Phantom VIII</t>
+          <t>Lamborghini Aventador SVJ</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
+          <t>output\master_vehicles_tracker_08_Lamborghini_Aventador_SVJ\Lamborghini_Aventador_SVJ.mp4</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -9198,17 +9198,17 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>BMW S1000RR M Package</t>
+          <t>Ducati Panigale V4 S</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
+          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -9238,17 +9238,17 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>BMW S1000RR M Package</t>
+          <t>Ducati Panigale V4 S</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
+          <t>output\master_vehicles_tracker_09_Ducati_Panigale_V4_S\Ducati_Panigale_V4_S.mp4</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -9278,17 +9278,17 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>Toyota Supra MK4 Turbo (A80)</t>
+          <t>Rolls Royce Phantom VIII</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
+          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -9318,17 +9318,17 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Toyota Supra MK4 Turbo (A80)</t>
+          <t>Rolls Royce Phantom VIII</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
+          <t>output\master_vehicles_tracker_10_Rolls_Royce_Phantom_VIII\Rolls_Royce_Phantom_VIII.mp4</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Hayabusa GSX1300R</t>
+          <t>BMW S1000RR M Package</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
+          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -9398,17 +9398,17 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Hayabusa GSX1300R</t>
+          <t>BMW S1000RR M Package</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
+          <t>output\master_vehicles_tracker_11_BMW_S1000RR_M_Package\BMW_S1000RR_M_Package.mp4</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -9438,17 +9438,17 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>Ferrari F40</t>
+          <t>Toyota Supra MK4 Turbo (A80)</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
+          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -9478,17 +9478,17 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Ferrari F40</t>
+          <t>Toyota Supra MK4 Turbo (A80)</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
+          <t>output\master_vehicles_tracker_12_Toyota_Supra_MK4_Turbo_(A80)\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -9518,17 +9518,17 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Fat Boy 114</t>
+          <t>Suzuki Hayabusa GSX1300R</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
+          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -9558,17 +9558,17 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Fat Boy 114</t>
+          <t>Suzuki Hayabusa GSX1300R</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
+          <t>output\master_vehicles_tracker_13_Suzuki_Hayabusa_GSX1300R\Suzuki_Hayabusa_GSX1300R.mp4</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -9598,17 +9598,17 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>McLaren P1</t>
+          <t>Ferrari F40</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
+          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -9638,17 +9638,17 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>McLaren P1</t>
+          <t>Ferrari F40</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
+          <t>output\master_vehicles_tracker_14_Ferrari_F40\Ferrari_F40.mp4</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -9678,17 +9678,17 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>KTM 390 Duke</t>
+          <t>Harley-Davidson Fat Boy 114</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
+          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -9718,17 +9718,17 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>KTM 390 Duke</t>
+          <t>Harley-Davidson Fat Boy 114</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
+          <t>output\master_vehicles_tracker_15_Harley-Davidson_Fat_Boy_114\Harley-Davidson_Fat_Boy_114.mp4</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -9758,17 +9758,17 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>Dodge Challenger SRT Demon 170</t>
+          <t>McLaren P1</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
+          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -9798,17 +9798,17 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Dodge Challenger SRT Demon 170</t>
+          <t>McLaren P1</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
+          <t>output\master_vehicles_tracker_16_McLaren_P1\McLaren_P1.mp4</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -9838,17 +9838,17 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>Yamaha YZF-R1M</t>
+          <t>KTM 390 Duke</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
+          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -9878,17 +9878,17 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Yamaha YZF-R1M</t>
+          <t>KTM 390 Duke</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
+          <t>output\master_vehicles_tracker_17_KTM_390_Duke\KTM_390_Duke.mp4</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -9918,17 +9918,17 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>Mercedes-AMG G63 Brabus 800</t>
+          <t>Dodge Challenger SRT Demon 170</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
+          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Mercedes-AMG G63 Brabus 800</t>
+          <t>Dodge Challenger SRT Demon 170</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
+          <t>output\master_vehicles_tracker_18_Dodge_Challenger_SRT_Demon_170\Dodge_Challenger_SRT_Demon_170.mp4</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -9998,22 +9998,22 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>Bugatti Chiron Super Sport 300+</t>
+          <t>Yamaha YZF-R1M</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
+          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -10038,22 +10038,22 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Bugatti Chiron Super Sport 300+</t>
+          <t>Yamaha YZF-R1M</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
+          <t>output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -10078,22 +10078,22 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja ZX-10R</t>
+          <t>Mercedes-AMG G63 Brabus 800</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
+          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -10118,22 +10118,22 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja ZX-10R</t>
+          <t>Mercedes-AMG G63 Brabus 800</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
+          <t>output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -10158,22 +10158,22 @@
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>Triumph Rocket 3 R</t>
+          <t>Bugatti Chiron Super Sport 300+</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
+          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -10198,22 +10198,22 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Triumph Rocket 3 R</t>
+          <t>Bugatti Chiron Super Sport 300+</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
+          <t>output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -10238,22 +10238,22 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Huracan STO</t>
+          <t>Kawasaki Ninja ZX-10R</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
+          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -10278,22 +10278,22 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Huracan STO</t>
+          <t>Kawasaki Ninja ZX-10R</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
+          <t>output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -10318,17 +10318,17 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>MV Agusta Superveloce 800</t>
+          <t>Triumph Rocket 3 R</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
+          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -10358,17 +10358,17 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>MV Agusta Superveloce 800</t>
+          <t>Triumph Rocket 3 R</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
+          <t>output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -10398,17 +10398,17 @@
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>Pagani Huayra BC</t>
+          <t>Lamborghini Huracan STO</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
+          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -10438,17 +10438,17 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>Pagani Huayra BC</t>
+          <t>Lamborghini Huracan STO</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
+          <t>output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>Aprilia RSV4 Factory 1100</t>
+          <t>MV Agusta Superveloce 800</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
+          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -10518,17 +10518,17 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Aprilia RSV4 Factory 1100</t>
+          <t>MV Agusta Superveloce 800</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
+          <t>output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -10558,17 +10558,17 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>Chevrolet Corvette Z06 (C8)</t>
+          <t>Pagani Huayra BC</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
+          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -10598,17 +10598,17 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>Chevrolet Corvette Z06 (C8)</t>
+          <t>Pagani Huayra BC</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
+          <t>output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -10638,17 +10638,17 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>Honda CBR1000RR-R Fireblade SP</t>
+          <t>Aprilia RSV4 Factory 1100</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
+          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -10678,17 +10678,17 @@
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Honda CBR1000RR-R Fireblade SP</t>
+          <t>Aprilia RSV4 Factory 1100</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
+          <t>output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -10718,17 +10718,17 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>Nissan GT-R Nismo (R35)</t>
+          <t>Chevrolet Corvette Z06 (C8)</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
+          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -10758,17 +10758,17 @@
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:26</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>Nissan GT-R Nismo (R35)</t>
+          <t>Chevrolet Corvette Z06 (C8)</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
+          <t>output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>BMW M1000RR</t>
+          <t>Honda CBR1000RR-R Fireblade SP</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
+          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -10838,17 +10838,17 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>BMW M1000RR</t>
+          <t>Honda CBR1000RR-R Fireblade SP</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
+          <t>output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -10878,17 +10878,17 @@
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>Ferrari LaFerrari</t>
+          <t>Nissan GT-R Nismo (R35)</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
+          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -10918,17 +10918,17 @@
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Ferrari LaFerrari</t>
+          <t>Nissan GT-R Nismo (R35)</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
+          <t>output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>KTM 1290 Super Duke R Evo</t>
+          <t>BMW M1000RR</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
+          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -10998,17 +10998,17 @@
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>KTM 1290 Super Duke R Evo</t>
+          <t>BMW M1000RR</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
+          <t>output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -11038,17 +11038,17 @@
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:44</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>Porsche 918 Spyder</t>
+          <t>Ferrari LaFerrari</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
+          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -11078,17 +11078,17 @@
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Porsche 918 Spyder</t>
+          <t>Ferrari LaFerrari</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
+          <t>output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -11118,17 +11118,17 @@
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Sportster S</t>
+          <t>KTM 1290 Super Duke R Evo</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
+          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -11158,17 +11158,17 @@
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Sportster S</t>
+          <t>KTM 1290 Super Duke R Evo</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
+          <t>output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -11198,17 +11198,17 @@
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>Shelby Cobra 427 S/C</t>
+          <t>Porsche 918 Spyder</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
+          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -11238,17 +11238,17 @@
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Shelby Cobra 427 S/C</t>
+          <t>Porsche 918 Spyder</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
+          <t>output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -11278,17 +11278,17 @@
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>Ducati Diavel V4</t>
+          <t>Harley-Davidson Sportster S</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
+          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -11318,17 +11318,17 @@
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Ducati Diavel V4</t>
+          <t>Harley-Davidson Sportster S</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
+          <t>output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -11358,17 +11358,17 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>Audi R8 V10 Performance</t>
+          <t>Shelby Cobra 427 S/C</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
+          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -11398,17 +11398,17 @@
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Audi R8 V10 Performance</t>
+          <t>Shelby Cobra 427 S/C</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
+          <t>output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -11438,17 +11438,17 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-10 SP</t>
+          <t>Ducati Diavel V4</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
+          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -11478,17 +11478,17 @@
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-10 SP</t>
+          <t>Ducati Diavel V4</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
+          <t>output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -11518,17 +11518,17 @@
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>Mazda RX-7 Spirit R (FD3S)</t>
+          <t>Audi R8 V10 Performance</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
+          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -11558,17 +11558,17 @@
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Mazda RX-7 Spirit R (FD3S)</t>
+          <t>Audi R8 V10 Performance</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
+          <t>output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -11598,17 +11598,17 @@
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z H2 Supercharged</t>
+          <t>Yamaha MT-10 SP</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
+          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -11638,17 +11638,17 @@
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z H2 Supercharged</t>
+          <t>Yamaha MT-10 SP</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
+          <t>output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -11678,17 +11678,17 @@
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>Lexus LFA Nurburgring Edition</t>
+          <t>Mazda RX-7 Spirit R (FD3S)</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -11718,17 +11718,17 @@
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Lexus LFA Nurburgring Edition</t>
+          <t>Mazda RX-7 Spirit R (FD3S)</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -11758,17 +11758,17 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Katana</t>
+          <t>Kawasaki Z H2 Supercharged</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -11798,17 +11798,17 @@
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Katana</t>
+          <t>Kawasaki Z H2 Supercharged</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+          <t>output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -11838,17 +11838,17 @@
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>McLaren 720S Spider</t>
+          <t>Lexus LFA Nurburgring Edition</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -11878,17 +11878,17 @@
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>McLaren 720S Spider</t>
+          <t>Lexus LFA Nurburgring Edition</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+          <t>output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -11918,17 +11918,17 @@
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>Honda CB1000R Black Edition</t>
+          <t>Suzuki Katana</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -11958,17 +11958,17 @@
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Honda CB1000R Black Edition</t>
+          <t>Suzuki Katana</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+          <t>output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -11998,17 +11998,17 @@
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Murcielago LP670-4 SV</t>
+          <t>McLaren 720S Spider</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -12038,17 +12038,17 @@
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Murcielago LP670-4 SV</t>
+          <t>McLaren 720S Spider</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+          <t>output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -12078,17 +12078,17 @@
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:29:15</t>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>Indian Scout Bobber</t>
+          <t>Honda CB1000R Black Edition</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
+          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -12118,47 +12118,207 @@
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21 00:12:27</t>
+          <t>2026-09-21 00:29:15</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB1000R Black Edition</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E292" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 18:05:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>Lamborghini Murcielago LP670-4 SV</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E293" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:29:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>Lamborghini Murcielago LP670-4 SV</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E294" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 18:05:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B292" s="3" t="inlineStr">
+      <c r="B295" s="3" t="inlineStr">
         <is>
           <t>Indian Scout Bobber</t>
         </is>
       </c>
-      <c r="C292" s="2" t="inlineStr">
+      <c r="C295" s="2" t="inlineStr">
         <is>
           <t>Motorcycle</t>
         </is>
       </c>
-      <c r="D292" s="2" t="inlineStr">
+      <c r="D295" s="2" t="inlineStr">
         <is>
           <t>master_vehicles_tracker</t>
         </is>
       </c>
-      <c r="E292" s="4" t="inlineStr">
-        <is>
-          <t>EDITED</t>
-        </is>
-      </c>
-      <c r="F292" s="3" t="inlineStr">
+      <c r="E295" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="inlineStr">
         <is>
           <t>output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
         </is>
       </c>
-      <c r="G292" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H292" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21 00:29:15</t>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:29:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>Indian Scout Bobber</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>master_vehicles_tracker</t>
+        </is>
+      </c>
+      <c r="E296" s="4" t="inlineStr">
+        <is>
+          <t>EDITED</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 18:05:45</t>
         </is>
       </c>
     </row>
